--- a/survey_templates/046_smart_glasses_feedback_form--survey_templates.xlsx
+++ b/survey_templates/046_smart_glasses_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'usa'}</t>
+          <t>usa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'USA'}</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'uk'}</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'UK'}</t>
+          <t>UK</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
